--- a/data/trans_orig/IP19C07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C07-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39857</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49600</t>
+          <t>49456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37547</t>
+          <t>37082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45857</t>
+          <t>45298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80114</t>
+          <t>81474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92965</t>
+          <t>93379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32348</t>
+          <t>32221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38942</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36417</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>66122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74616</t>
+          <t>74283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32064</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44901</t>
+          <t>44857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51434</t>
+          <t>51482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>72343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82028</t>
+          <t>82255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16413</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82645</t>
+          <t>82763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93110</t>
+          <t>93000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76193</t>
+          <t>75606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87489</t>
+          <t>87428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163665</t>
+          <t>163470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177878</t>
+          <t>178246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46569</t>
+          <t>46126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53166</t>
+          <t>52693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61717</t>
+          <t>61488</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68091</t>
+          <t>68457</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110317</t>
+          <t>111057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120147</t>
+          <t>120165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26470</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>35462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35071</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59062</t>
+          <t>59229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68672</t>
+          <t>69001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31757</t>
+          <t>31656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50950</t>
+          <t>51695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25696</t>
+          <t>26202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43056</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63252</t>
+          <t>63049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88019</t>
+          <t>88661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>272148</t>
+          <t>271403</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291341</t>
+          <t>291442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298632</t>
+          <t>297479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315992</t>
+          <t>315486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>576767</t>
+          <t>576125</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>601534</t>
+          <t>601737</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>43645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38066</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68762</t>
+          <t>68561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80185</t>
+          <t>80030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>18412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>44999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50055</t>
+          <t>49689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82832</t>
+          <t>82157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93255</t>
+          <t>93434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39002</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33899</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39156</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67836</t>
+          <t>67914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76716</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80167</t>
+          <t>80418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88534</t>
+          <t>88145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89297</t>
+          <t>88406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96027</t>
+          <t>96012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172708</t>
+          <t>172748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182839</t>
+          <t>182678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75597</t>
+          <t>75984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81537</t>
+          <t>81535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59310</t>
+          <t>59475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69370</t>
+          <t>69410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138117</t>
+          <t>138729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149330</t>
+          <t>149390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23625</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24654</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33425</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44923</t>
+          <t>44616</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55160</t>
+          <t>55252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>25405</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43357</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44904</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57219</t>
+          <t>56237</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84650</t>
+          <t>81815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>293984</t>
+          <t>293792</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312006</t>
+          <t>311936</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297995</t>
+          <t>297065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316244</t>
+          <t>316983</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>595590</t>
+          <t>598425</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>623021</t>
+          <t>624003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>34151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>41622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>40234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47918</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77273</t>
+          <t>77758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88164</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45748</t>
+          <t>45819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53080</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50418</t>
+          <t>50376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98552</t>
+          <t>98097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106856</t>
+          <t>106504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>24606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57267</t>
+          <t>56441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64471</t>
+          <t>64247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98941</t>
+          <t>98756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107990</t>
+          <t>108193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92458</t>
+          <t>92278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100768</t>
+          <t>100841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>194026</t>
+          <t>195420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207123</t>
+          <t>206820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56517</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65224</t>
+          <t>65232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64186</t>
+          <t>64588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71808</t>
+          <t>71762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124966</t>
+          <t>124429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>135766</t>
+          <t>135903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>25697</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>31927</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31462</t>
+          <t>31520</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54161</t>
+          <t>54131</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62041</t>
+          <t>62146</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39638</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63036</t>
+          <t>63213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>304587</t>
+          <t>303958</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>321776</t>
+          <t>321859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319066</t>
+          <t>319644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>333597</t>
+          <t>334206</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>628966</t>
+          <t>628789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>652364</t>
+          <t>651999</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>23367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57663</t>
+          <t>58118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>67731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82790</t>
+          <t>83524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92368</t>
+          <t>92688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145139</t>
+          <t>144497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158291</t>
+          <t>158402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23319</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47278</t>
+          <t>46810</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57323</t>
+          <t>57378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59630</t>
+          <t>60659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>68814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110970</t>
+          <t>111189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124300</t>
+          <t>124364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>21729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26888</t>
+          <t>27668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34778</t>
+          <t>34816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52445</t>
+          <t>51350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61528</t>
+          <t>61069</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100429</t>
+          <t>101092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108570</t>
+          <t>108572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114866</t>
+          <t>114718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125304</t>
+          <t>125443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218938</t>
+          <t>220106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231845</t>
+          <t>232421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12012</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59606</t>
+          <t>60766</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67217</t>
+          <t>67558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95947</t>
+          <t>95300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102576</t>
+          <t>102532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>159686</t>
+          <t>160097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169038</t>
+          <t>169161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>871</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>37480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>38254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80056</t>
+          <t>80348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88117</t>
+          <t>88128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>22388</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40437</t>
+          <t>40492</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>39582</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>72984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>346376</t>
+          <t>346321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>365009</t>
+          <t>364425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>439925</t>
+          <t>439083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>459463</t>
+          <t>459234</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>793937</t>
+          <t>792494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>820291</t>
+          <t>820035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
